--- a/survey_templates/017_haircare_routine_quiz--survey_templates.xlsx
+++ b/survey_templates/017_haircare_routine_quiz--survey_templates.xlsx
@@ -1,15 +1,15 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
   <workbookProtection/>
   <bookViews>
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet name="survey" sheetId="1" state="visible" r:id="rId1"/>
-    <sheet name="choices" sheetId="2" state="visible" r:id="rId2"/>
-    <sheet name="settings" sheetId="3" state="visible" r:id="rId3"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="survey" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="choices" sheetId="2" state="visible" r:id="rId2"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="settings" sheetId="3" state="visible" r:id="rId3"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -734,8 +734,8 @@
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="26" customWidth="1" min="1" max="1"/>
-    <col width="50" customWidth="1" min="2" max="2"/>
-    <col width="50" customWidth="1" min="3" max="3"/>
+    <col width="9" customWidth="1" min="2" max="2"/>
+    <col width="9" customWidth="1" min="3" max="3"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -763,12 +763,12 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>{'id':_10,_'name':_'normal',_'label':_'normal'}</t>
+          <t>normal</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>{'id': 10, 'name': 'normal', 'label': 'normal'}</t>
+          <t>normal</t>
         </is>
       </c>
     </row>
@@ -780,12 +780,12 @@
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>{'id':_20,_'name':_'wavy',_'label':_'wavy'}</t>
+          <t>wavy</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>{'id': 20, 'name': 'wavy', 'label': 'wavy'}</t>
+          <t>wavy</t>
         </is>
       </c>
     </row>
@@ -797,12 +797,12 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>{'id':_30,_'name':_'curly',_'label':_'curly'}</t>
+          <t>curly</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>{'id': 30, 'name': 'curly', 'label': 'curly'}</t>
+          <t>curly</t>
         </is>
       </c>
     </row>
@@ -814,12 +814,12 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>{'id':_40,_'name':_'normal',_'label':_'normal'}</t>
+          <t>normal</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>{'id': 40, 'name': 'normal', 'label': 'normal'}</t>
+          <t>normal</t>
         </is>
       </c>
     </row>
@@ -831,12 +831,12 @@
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>{'id':_50,_'name':_'dry',_'label':_'dry'}</t>
+          <t>dry</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>{'id': 50, 'name': 'dry', 'label': 'dry'}</t>
+          <t>dry</t>
         </is>
       </c>
     </row>
@@ -848,12 +848,12 @@
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>{'id':_60,_'name':_'damaged',_'label':_'damaged'}</t>
+          <t>damaged</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>{'id': 60, 'name': 'damaged', 'label': 'damaged'}</t>
+          <t>damaged</t>
         </is>
       </c>
     </row>
@@ -865,12 +865,12 @@
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>{'id':_70,_'name':_'black',_'label':_'black'}</t>
+          <t>black</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>{'id': 70, 'name': 'black', 'label': 'black'}</t>
+          <t>black</t>
         </is>
       </c>
     </row>
@@ -882,12 +882,12 @@
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>{'id':_80,_'name':_'blonde',_'label':_'blonde'}</t>
+          <t>blonde</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>{'id': 80, 'name': 'blonde', 'label': 'blonde'}</t>
+          <t>blonde</t>
         </is>
       </c>
     </row>
@@ -899,12 +899,12 @@
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>{'id':_90,_'name':_'red',_'label':_'red'}</t>
+          <t>red</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>{'id': 90, 'name': 'red', 'label': 'red'}</t>
+          <t>red</t>
         </is>
       </c>
     </row>
@@ -916,12 +916,12 @@
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>{'id':_100,_'name':_'short',_'label':_'short'}</t>
+          <t>short</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>{'id': 100, 'name': 'short', 'label': 'short'}</t>
+          <t>short</t>
         </is>
       </c>
     </row>
@@ -933,12 +933,12 @@
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>{'id':_110,_'name':_'medium',_'label':_'medium'}</t>
+          <t>medium</t>
         </is>
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>{'id': 110, 'name': 'medium', 'label': 'medium'}</t>
+          <t>medium</t>
         </is>
       </c>
     </row>
@@ -950,12 +950,12 @@
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>{'id':_120,_'name':_'long',_'label':_'long'}</t>
+          <t>long</t>
         </is>
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>{'id': 120, 'name': 'long', 'label': 'long'}</t>
+          <t>long</t>
         </is>
       </c>
     </row>
